--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationtiming.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationtiming.xlsx
@@ -661,7 +661,7 @@
     <t>既知 /定義されたタイミングパターンのコード。 / Code for a known / defined timing pattern.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation</t>
+    <t>http://hl7.org/fhir/ValueSet/timing-abbreviation|4.0.1</t>
   </si>
   <si>
     <t>QSC.code</t>
@@ -996,7 +996,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="56.81640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.51171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
